--- a/ARM Functions/Ability Edits/Emergency Exit.xlsx
+++ b/ARM Functions/Ability Edits/Emergency Exit.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F383FA83-123F-4167-932D-7D80C20B20D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{437C05EF-85EA-47BF-9799-64D8889AB0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31689" yWindow="5897" windowWidth="24686" windowHeight="13149" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Edited" sheetId="6" r:id="rId1"/>
     <sheet name="original" sheetId="12" r:id="rId2"/>
     <sheet name="Table of IDs" sheetId="11" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="1305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="1305">
   <si>
     <t>Address</t>
   </si>
@@ -3589,9 +3589,6 @@
     <t>get pointer</t>
   </si>
   <si>
-    <t>check if current HP 0</t>
-  </si>
-  <si>
     <t>mov r1, 0xE</t>
   </si>
   <si>
@@ -3628,12 +3625,6 @@
     <t>b 0x0007CCF4</t>
   </si>
   <si>
-    <t>bl 0x000938E8</t>
-  </si>
-  <si>
-    <t>00101970</t>
-  </si>
-  <si>
     <t>F0432DE9</t>
   </si>
   <si>
@@ -3802,27 +3793,12 @@
     <t>Emergency Exit End of turn switch + Regenerator 0x8F</t>
   </si>
   <si>
-    <t>7318FEEB</t>
-  </si>
-  <si>
-    <t>3E42FEEB</t>
-  </si>
-  <si>
     <t>0090A0E1</t>
   </si>
   <si>
-    <t>D047FEEB</t>
-  </si>
-  <si>
     <t>0900A0E1</t>
   </si>
   <si>
-    <t>1B43FEEB</t>
-  </si>
-  <si>
-    <t>1743FEEB</t>
-  </si>
-  <si>
     <t>A40050E1</t>
   </si>
   <si>
@@ -3832,21 +3808,12 @@
     <t>0510A0E3</t>
   </si>
   <si>
-    <t>F7F7FDEB</t>
-  </si>
-  <si>
     <t>0090A081</t>
   </si>
   <si>
     <t>0090A091</t>
   </si>
   <si>
-    <t>DB26FEEB</t>
-  </si>
-  <si>
-    <t>3B17FEEB</t>
-  </si>
-  <si>
     <t>4C50C0E5</t>
   </si>
   <si>
@@ -3901,58 +3868,91 @@
     <t>0C9080E5</t>
   </si>
   <si>
-    <t>B2ECFDEB</t>
-  </si>
-  <si>
     <t>B42ADFE1</t>
   </si>
   <si>
-    <t>FB20FEEB</t>
-  </si>
-  <si>
-    <t>2B17FEEB</t>
-  </si>
-  <si>
-    <t>8220FEEB</t>
-  </si>
-  <si>
-    <t>65F7FDEB</t>
-  </si>
-  <si>
-    <t>62F7FDEB</t>
-  </si>
-  <si>
-    <t>9BECFDEB</t>
-  </si>
-  <si>
     <t>bl 0x00089E28</t>
   </si>
   <si>
     <t>unshow Ability Banner?</t>
   </si>
   <si>
-    <t>5900001A</t>
-  </si>
-  <si>
-    <t>5200001A</t>
-  </si>
-  <si>
     <t>4900008A</t>
   </si>
   <si>
-    <t>E420FEEB</t>
-  </si>
-  <si>
-    <t>1417FEEB</t>
-  </si>
-  <si>
-    <t>FA43FEEB</t>
-  </si>
-  <si>
-    <t>7EECFDEA</t>
-  </si>
-  <si>
     <t>F4070000</t>
+  </si>
+  <si>
+    <t>bl 0x000611C0</t>
+  </si>
+  <si>
+    <t>Check if any Pokemon to switch with</t>
+  </si>
+  <si>
+    <t>00103B80</t>
+  </si>
+  <si>
+    <t>EF0FFEEB</t>
+  </si>
+  <si>
+    <t>BA39FEEB</t>
+  </si>
+  <si>
+    <t>5200000A</t>
+  </si>
+  <si>
+    <t>5B00001A</t>
+  </si>
+  <si>
+    <t>8075FDEB</t>
+  </si>
+  <si>
+    <t>953AFEEB</t>
+  </si>
+  <si>
+    <t>913AFEEB</t>
+  </si>
+  <si>
+    <t>71EFFDEB</t>
+  </si>
+  <si>
+    <t>551EFEEB</t>
+  </si>
+  <si>
+    <t>B50EFEEB</t>
+  </si>
+  <si>
+    <t>2CE4FDEB</t>
+  </si>
+  <si>
+    <t>7518FEEB</t>
+  </si>
+  <si>
+    <t>A50EFEEB</t>
+  </si>
+  <si>
+    <t>FC17FEEB</t>
+  </si>
+  <si>
+    <t>DFEEFDEB</t>
+  </si>
+  <si>
+    <t>DCEEFDEB</t>
+  </si>
+  <si>
+    <t>15E4FDEB</t>
+  </si>
+  <si>
+    <t>5E18FEEB</t>
+  </si>
+  <si>
+    <t>8E0EFEEB</t>
+  </si>
+  <si>
+    <t>743BFEEB</t>
+  </si>
+  <si>
+    <t>F8E3FDEA</t>
   </si>
 </sst>
 </file>
@@ -4496,7 +4496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr defaultColWidth="9.0703125" defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="8" customWidth="1"/>
@@ -4543,7 +4543,7 @@
         <v>0110A0E3</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4604,24 +4604,24 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="7" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="8" t="s">
-        <v>1197</v>
+        <v>1283</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="8" t="str">
-        <f t="shared" ref="A12:A75" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
-        <v>00101974</v>
+        <f t="shared" ref="A12:A77" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
+        <v>00103B84</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>1066</v>
@@ -4633,7 +4633,7 @@
     <row r="13" spans="1:13">
       <c r="A13" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>00101978</v>
+        <v>00103B88</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>867</v>
@@ -4645,7 +4645,7 @@
     <row r="14" spans="1:13">
       <c r="A14" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>0010197C</v>
+        <v>00103B8C</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>1111</v>
@@ -4657,7 +4657,7 @@
     <row r="15" spans="1:13">
       <c r="A15" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>00101980</v>
+        <v>00103B90</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>869</v>
@@ -4672,10 +4672,10 @@
     <row r="16" spans="1:13">
       <c r="A16" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>00101984</v>
+        <v>00103B94</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>1254</v>
+        <v>1284</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>1179</v>
@@ -4685,7 +4685,7 @@
     <row r="17" spans="1:5">
       <c r="A17" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>00101988</v>
+        <v>00103B98</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>870</v>
@@ -4698,21 +4698,21 @@
     <row r="18" spans="1:5">
       <c r="A18" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>0010198C</v>
+        <v>00103B9C</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>1297</v>
+        <v>1287</v>
       </c>
       <c r="C18" s="13" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A109)</f>
-        <v>bne 0x00101AF8</v>
+        <f>_xlfn.CONCAT("bne 0x",A111)</f>
+        <v>bne 0x00103D10</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>00101990</v>
+        <v>00103BA0</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>876</v>
@@ -4727,7 +4727,7 @@
     <row r="20" spans="1:5">
       <c r="A20" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>00101994</v>
+        <v>00103BA4</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>856</v>
@@ -4740,10 +4740,10 @@
     <row r="21" spans="1:5">
       <c r="A21" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>00101998</v>
+        <v>00103BA8</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>1255</v>
+        <v>1285</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>1181</v>
@@ -4751,1248 +4751,1274 @@
       <c r="D21" s="15"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="16" t="str">
+      <c r="A22" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>0010199C</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>1210</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>1183</v>
-      </c>
+        <v>00103BAC</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D22" s="15"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>001019A0</v>
+        <v>00103BB0</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>1257</v>
+        <v>876</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>1196</v>
-      </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="9"/>
+        <v>875</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>1282</v>
+      </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>001019A4</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>855</v>
+        <v>00103BB4</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>856</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>1177</v>
+        <v>848</v>
       </c>
       <c r="D24" s="16"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>001019A8</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C25" s="16" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A109)</f>
-        <v>bne 0x00101AF8</v>
+        <v>00103BB8</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>1281</v>
       </c>
       <c r="D25" s="16"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="19" t="str">
+      <c r="A26" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>001019AC</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>1203</v>
-      </c>
+        <v>00103BBC</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>855</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D26" s="16"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="19" t="str">
+      <c r="A27" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>001019B0</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D27" s="19"/>
+        <v>00103BC0</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C27" s="16" t="str">
+        <f>_xlfn.CONCAT("beq 0x",A111)</f>
+        <v>beq 0x00103D10</v>
+      </c>
+      <c r="D27" s="16"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019B4</v>
+        <v>00103BC4</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>1259</v>
+        <v>1162</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D28" s="19"/>
+        <v>1183</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>1200</v>
+      </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019B8</v>
+        <v>00103BC8</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>938</v>
+        <v>1252</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>902</v>
+        <v>1208</v>
       </c>
       <c r="D29" s="19"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019BC</v>
+        <v>00103BCC</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>939</v>
+        <v>1289</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="D30" s="19"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019C0</v>
+        <v>00103BD0</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>1258</v>
+        <v>938</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>1211</v>
+        <v>902</v>
       </c>
       <c r="D31" s="19"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019C4</v>
+        <v>00103BD4</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>1260</v>
+        <v>939</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>1202</v>
-      </c>
+        <v>1184</v>
+      </c>
+      <c r="D32" s="19"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019C8</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>1261</v>
+        <v>00103BD8</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>1252</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>1208</v>
       </c>
-      <c r="D33" s="19" t="s">
-        <v>1204</v>
-      </c>
+      <c r="D33" s="19"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019CC</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>1299</v>
-      </c>
-      <c r="C34" s="19" t="str">
-        <f>_xlfn.CONCAT("bhi 0x",A109)</f>
-        <v>bhi 0x00101AF8</v>
+        <v>00103BDC</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>1192</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019D0</v>
+        <v>00103BE0</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>1262</v>
+        <v>1253</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>1201</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="18" t="str">
+      <c r="A36" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019D4</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D36" s="18"/>
+        <v>00103BE4</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C36" s="19" t="str">
+        <f>_xlfn.CONCAT("bhi 0x",A111)</f>
+        <v>bhi 0x00103D10</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>1202</v>
+      </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="18" t="str">
+      <c r="A37" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>001019D8</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>1263</v>
-      </c>
-      <c r="C37" s="18" t="s">
+        <v>00103BE8</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>1206</v>
       </c>
-      <c r="D37" s="18" t="s">
-        <v>1207</v>
+      <c r="D37" s="19" t="s">
+        <v>1198</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="18" t="str">
         <f t="shared" si="1"/>
-        <v>001019DC</v>
+        <v>00103BEC</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>1264</v>
+        <v>1252</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>1192</v>
+        <v>1208</v>
       </c>
       <c r="D38" s="18"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="21" t="str">
+      <c r="A39" s="18" t="str">
         <f t="shared" si="1"/>
-        <v>001019E0</v>
-      </c>
-      <c r="B39" s="22" t="s">
-        <v>941</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>905</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>1214</v>
+        <v>00103BF0</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>1204</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="21" t="str">
+      <c r="A40" s="18" t="str">
         <f t="shared" si="1"/>
-        <v>001019E4</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D40" s="21"/>
+        <v>00103BF4</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D40" s="18"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="21" t="str">
         <f t="shared" si="1"/>
-        <v>001019E8</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>1266</v>
+        <v>00103BF8</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>941</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D41" s="21"/>
+        <v>905</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>1211</v>
+      </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="24" t="str">
+      <c r="A42" s="21" t="str">
         <f t="shared" si="1"/>
-        <v>001019EC</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>861</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>833</v>
-      </c>
-      <c r="D42" s="24" t="s">
-        <v>1216</v>
-      </c>
+        <v>00103BFC</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D42" s="21"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="24" t="str">
+      <c r="A43" s="21" t="str">
         <f t="shared" si="1"/>
-        <v>001019F0</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C43" s="24" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E43)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x0008B564</v>
-      </c>
-      <c r="D43" s="24"/>
-      <c r="E43" s="8">
-        <v>768564</v>
-      </c>
+        <v>00103C00</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D43" s="21"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>001019F4</v>
+        <v>00103C04</v>
       </c>
       <c r="B44" s="24" t="s">
+        <v>861</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>833</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C08</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C45" s="24" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E45)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x0008B564</v>
+      </c>
+      <c r="D45" s="24"/>
+      <c r="E45" s="8">
+        <v>768564</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C0C</v>
+      </c>
+      <c r="B46" s="24" t="s">
         <v>1042</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C46" s="24" t="s">
         <v>992</v>
       </c>
-      <c r="D44" s="24"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v>001019F8</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>970</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v>001019FC</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>880</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>879</v>
-      </c>
-      <c r="D46" s="23"/>
+      <c r="D46" s="24"/>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A00</v>
+        <v>00103C10</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>856</v>
+        <v>1009</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>848</v>
-      </c>
-      <c r="D47" s="23"/>
+        <v>970</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>1189</v>
+      </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A04</v>
+        <v>00103C14</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>1268</v>
+        <v>880</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>1194</v>
+        <v>879</v>
       </c>
       <c r="D48" s="23"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A08</v>
+        <v>00103C18</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>1168</v>
+        <v>856</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>1186</v>
+        <v>848</v>
       </c>
       <c r="D49" s="23"/>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A0C</v>
+        <v>00103C1C</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>1169</v>
+        <v>1293</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="D50" s="23"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A10</v>
+        <v>00103C20</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="D51" s="23"/>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A14</v>
+        <v>00103C24</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>1286</v>
+        <v>1169</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>1215</v>
+        <v>1186</v>
       </c>
       <c r="D52" s="23"/>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A18</v>
+        <v>00103C28</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>1012</v>
+        <v>1170</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>973</v>
+        <v>1187</v>
       </c>
       <c r="D53" s="23"/>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A1C</v>
+        <v>00103C2C</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>1172</v>
+        <v>1275</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>1189</v>
+        <v>1212</v>
       </c>
       <c r="D54" s="23"/>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A20</v>
+        <v>00103C30</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>856</v>
+        <v>1012</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>848</v>
+        <v>973</v>
       </c>
       <c r="D55" s="23"/>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A24</v>
+        <v>00103C34</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>1287</v>
+        <v>1172</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>1250</v>
+        <v>1188</v>
       </c>
       <c r="D56" s="23"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="30" t="str">
+      <c r="A57" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A28</v>
-      </c>
-      <c r="B57" s="30" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C57" s="30" t="s">
-        <v>970</v>
-      </c>
-      <c r="D57" s="30" t="s">
-        <v>1233</v>
-      </c>
+        <v>00103C38</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>856</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>848</v>
+      </c>
+      <c r="D57" s="23"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="30" t="str">
+      <c r="A58" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>00101A2C</v>
-      </c>
-      <c r="B58" s="30" t="s">
-        <v>862</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>1252</v>
-      </c>
-      <c r="D58" s="30"/>
+        <v>00103C3C</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D58" s="23"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>00101A30</v>
+        <v>00103C40</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>856</v>
+        <v>1009</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>848</v>
-      </c>
-      <c r="D59" s="30"/>
+        <v>970</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>1230</v>
+      </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="30" t="str">
         <f t="shared" si="1"/>
-        <v>00101A34</v>
+        <v>00103C44</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>1289</v>
-      </c>
-      <c r="C60" s="30" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E60)-HEX2DEC("6dd000"),8))</f>
+        <v>862</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D60" s="30"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C48</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>856</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>848</v>
+      </c>
+      <c r="D61" s="30"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C4C</v>
+      </c>
+      <c r="B62" s="30" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C62" s="30" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E62)-HEX2DEC("6dd000"),8))</f>
         <v>bl 0x00089E28</v>
       </c>
-      <c r="D60" s="30"/>
-      <c r="E60" s="9" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="25" t="str">
-        <f t="shared" si="1"/>
-        <v>00101A38</v>
-      </c>
-      <c r="B61" s="25" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>970</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="25" t="str">
-        <f t="shared" si="1"/>
-        <v>00101A3C</v>
-      </c>
-      <c r="B62" s="25" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D62" s="25"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="9" t="s">
+        <v>1229</v>
+      </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="25" t="str">
         <f t="shared" si="1"/>
-        <v>00101A40</v>
+        <v>00103C50</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>856</v>
+        <v>1009</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>848</v>
-      </c>
-      <c r="D63" s="25"/>
+        <v>970</v>
+      </c>
+      <c r="D63" s="25" t="s">
+        <v>1216</v>
+      </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="25" t="str">
         <f t="shared" si="1"/>
-        <v>00101A44</v>
+        <v>00103C54</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C64" s="25" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E64)-HEX2DEC("6dd000"),8))</f>
-        <v>bl 0x000876F8</v>
+        <v>1010</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>1214</v>
       </c>
       <c r="D64" s="25"/>
-      <c r="E64" s="8" t="s">
-        <v>1218</v>
-      </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="25" t="str">
         <f t="shared" si="1"/>
-        <v>00101A48</v>
+        <v>00103C58</v>
       </c>
       <c r="B65" s="25" t="s">
+        <v>856</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>848</v>
+      </c>
+      <c r="D65" s="25"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C5C</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C66" s="25" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E66)-HEX2DEC("6dd000"),8))</f>
+        <v>bl 0x000876F8</v>
+      </c>
+      <c r="D66" s="25"/>
+      <c r="E66" s="8" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="25" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C60</v>
+      </c>
+      <c r="B67" s="25" t="s">
         <v>938</v>
       </c>
-      <c r="C65" s="25" t="s">
+      <c r="C67" s="25" t="s">
         <v>902</v>
       </c>
-      <c r="D65" s="25"/>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>00101A4C</v>
-      </c>
-      <c r="B66" s="26" t="s">
-        <v>1269</v>
-      </c>
-      <c r="C66" s="26" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D66" s="26" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>00101A50</v>
-      </c>
-      <c r="B67" s="26" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C67" s="26" t="str">
-        <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A110)-HEX2DEC(A67)-8,"]")</f>
-        <v>ldrh r2, [pc, #164]</v>
-      </c>
-      <c r="D67" s="26"/>
+      <c r="D67" s="25"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="26" t="str">
         <f t="shared" si="1"/>
-        <v>00101A54</v>
+        <v>00103C64</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>936</v>
+        <v>1258</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D68" s="26"/>
+        <v>1217</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>1218</v>
+      </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="26" t="str">
         <f t="shared" si="1"/>
-        <v>00101A58</v>
-      </c>
-      <c r="B69" s="33" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C69" s="26" t="s">
-        <v>1222</v>
+        <v>00103C68</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C69" s="26" t="str">
+        <f>_xlfn.CONCAT("ldrh r2, [pc, #",HEX2DEC(A112)-HEX2DEC(A69)-8,"]")</f>
+        <v>ldrh r2, [pc, #164]</v>
       </c>
       <c r="D69" s="26"/>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="26" t="str">
         <f t="shared" si="1"/>
-        <v>00101A5C</v>
+        <v>00103C6C</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C70" s="26" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E70)-HEX2DEC("6dd000"),8))</f>
+        <v>936</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D70" s="26"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C70</v>
+      </c>
+      <c r="B71" s="33" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D71" s="26"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="26" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C74</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C72" s="26" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E72)-HEX2DEC("6dd000"),8))</f>
         <v>bl 0x00089C6C</v>
       </c>
-      <c r="D70" s="26"/>
-      <c r="E70" s="8" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>00101A60</v>
-      </c>
-      <c r="B71" s="27" t="s">
-        <v>876</v>
-      </c>
-      <c r="C71" s="27" t="s">
-        <v>875</v>
-      </c>
-      <c r="D71" s="27" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>00101A64</v>
-      </c>
-      <c r="B72" s="34" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C72" s="27" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D72" s="27"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="8" t="s">
+        <v>1220</v>
+      </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="27" t="str">
         <f t="shared" si="1"/>
-        <v>00101A68</v>
+        <v>00103C78</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C73" s="27" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E73)-HEX2DEC("6dd000"),8))</f>
+        <v>876</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>875</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C7C</v>
+      </c>
+      <c r="B74" s="34" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C74" s="27" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D74" s="27"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C80</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C75" s="27" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E75)-HEX2DEC("6dd000"),8))</f>
         <v>bl 0x0007F804</v>
       </c>
-      <c r="D73" s="27"/>
-      <c r="E73" s="8" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>00101A6C</v>
-      </c>
-      <c r="B74" s="28" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C74" s="28" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D74" s="28" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>00101A70</v>
-      </c>
-      <c r="B75" s="35" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C75" s="28" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D75" s="28"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="8" t="s">
+        <v>1222</v>
+      </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="28" t="str">
-        <f t="shared" ref="A76:A110" si="2">DEC2HEX(HEX2DEC(A75)+4,8)</f>
-        <v>00101A74</v>
+        <f t="shared" si="1"/>
+        <v>00103C84</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>1293</v>
+        <v>1261</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D76" s="28"/>
+        <v>1224</v>
+      </c>
+      <c r="D76" s="28" t="s">
+        <v>1226</v>
+      </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="29" t="str">
-        <f t="shared" si="2"/>
-        <v>00101A78</v>
-      </c>
-      <c r="B77" s="29" t="s">
-        <v>860</v>
-      </c>
-      <c r="C77" s="29" t="s">
-        <v>834</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>1231</v>
-      </c>
+      <c r="A77" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>00103C88</v>
+      </c>
+      <c r="B77" s="35" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D77" s="28"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="29" t="str">
-        <f t="shared" si="2"/>
-        <v>00101A7C</v>
-      </c>
-      <c r="B78" s="29" t="s">
-        <v>856</v>
-      </c>
-      <c r="C78" s="29" t="s">
-        <v>848</v>
-      </c>
-      <c r="D78" s="29"/>
+      <c r="A78" s="28" t="str">
+        <f t="shared" ref="A78:A112" si="2">DEC2HEX(HEX2DEC(A77)+4,8)</f>
+        <v>00103C8C</v>
+      </c>
+      <c r="B78" s="28" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C78" s="28" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D78" s="28"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>00101A80</v>
+        <v>00103C90</v>
       </c>
       <c r="B79" s="29" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C79" s="29" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E79)-HEX2DEC("6dd000"),8))</f>
+        <v>860</v>
+      </c>
+      <c r="C79" s="29" t="s">
+        <v>834</v>
+      </c>
+      <c r="D79" s="29" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v>00103C94</v>
+      </c>
+      <c r="B80" s="29" t="s">
+        <v>856</v>
+      </c>
+      <c r="C80" s="29" t="s">
+        <v>848</v>
+      </c>
+      <c r="D80" s="29"/>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v>00103C98</v>
+      </c>
+      <c r="B81" s="29" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C81" s="29" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E81)-HEX2DEC("6dd000"),8))</f>
         <v>bl 0x0007CCF4</v>
       </c>
-      <c r="D79" s="29"/>
-      <c r="E79" s="8" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>00101A84</v>
-      </c>
-      <c r="B80" s="30" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C80" s="30" t="s">
-        <v>970</v>
-      </c>
-      <c r="D80" s="30" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>00101A88</v>
-      </c>
-      <c r="B81" s="30" t="s">
-        <v>936</v>
-      </c>
-      <c r="C81" s="30" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D81" s="30"/>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="D81" s="29"/>
+      <c r="E81" s="8" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>00101A8C</v>
+        <v>00103C9C</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>856</v>
+        <v>1009</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>848</v>
-      </c>
-      <c r="D82" s="30"/>
-    </row>
-    <row r="83" spans="1:4">
+        <v>970</v>
+      </c>
+      <c r="D82" s="30" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>00101A90</v>
+        <v>00103CA0</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>1300</v>
+        <v>936</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>1295</v>
+        <v>1176</v>
       </c>
       <c r="D83" s="30"/>
     </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="31" t="str">
+    <row r="84" spans="1:5">
+      <c r="A84" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>00101A94</v>
-      </c>
-      <c r="B84" s="31" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C84" s="31" t="s">
-        <v>970</v>
-      </c>
-      <c r="D84" s="31" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="31" t="str">
+        <v>00103CA4</v>
+      </c>
+      <c r="B84" s="30" t="s">
+        <v>856</v>
+      </c>
+      <c r="C84" s="30" t="s">
+        <v>848</v>
+      </c>
+      <c r="D84" s="30"/>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>00101A98</v>
-      </c>
-      <c r="B85" s="31" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C85" s="31" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D85" s="31"/>
-    </row>
-    <row r="86" spans="1:4">
+        <v>00103CA8</v>
+      </c>
+      <c r="B85" s="30" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C85" s="30" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D85" s="30"/>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>00101A9C</v>
+        <v>00103CAC</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>856</v>
+        <v>1009</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>848</v>
-      </c>
-      <c r="D86" s="31"/>
-    </row>
-    <row r="87" spans="1:4">
+        <v>970</v>
+      </c>
+      <c r="D86" s="31" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>00101AA0</v>
+        <v>00103CB0</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>1301</v>
+        <v>1262</v>
       </c>
       <c r="C87" s="31" t="s">
-        <v>1194</v>
+        <v>1231</v>
       </c>
       <c r="D87" s="31"/>
     </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="32" t="str">
+    <row r="88" spans="1:5">
+      <c r="A88" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>00101AA4</v>
-      </c>
-      <c r="B88" s="32" t="s">
-        <v>938</v>
-      </c>
-      <c r="C88" s="32" t="s">
-        <v>902</v>
-      </c>
-      <c r="D88" s="32" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="32" t="str">
+        <v>00103CB4</v>
+      </c>
+      <c r="B88" s="31" t="s">
+        <v>856</v>
+      </c>
+      <c r="C88" s="31" t="s">
+        <v>848</v>
+      </c>
+      <c r="D88" s="31"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="31" t="str">
         <f t="shared" si="2"/>
-        <v>00101AA8</v>
-      </c>
-      <c r="B89" s="32" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C89" s="32" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D89" s="32"/>
-    </row>
-    <row r="90" spans="1:4">
+        <v>00103CB8</v>
+      </c>
+      <c r="B89" s="31" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C89" s="31" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D89" s="31"/>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>00101AAC</v>
+        <v>00103CBC</v>
       </c>
       <c r="B90" s="32" t="s">
-        <v>1274</v>
+        <v>938</v>
       </c>
       <c r="C90" s="32" t="s">
-        <v>1236</v>
-      </c>
-      <c r="D90" s="32"/>
-    </row>
-    <row r="91" spans="1:4">
+        <v>902</v>
+      </c>
+      <c r="D90" s="32" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>00101AB0</v>
+        <v>00103CC0</v>
       </c>
       <c r="B91" s="32" t="s">
-        <v>1275</v>
+        <v>1157</v>
       </c>
       <c r="C91" s="32" t="s">
-        <v>1237</v>
+        <v>1139</v>
       </c>
       <c r="D91" s="32"/>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:5">
       <c r="A92" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>00101AB4</v>
-      </c>
-      <c r="B92" s="36" t="s">
-        <v>1276</v>
+        <v>00103CC4</v>
+      </c>
+      <c r="B92" s="32" t="s">
+        <v>1263</v>
       </c>
       <c r="C92" s="32" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="D92" s="32"/>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:5">
       <c r="A93" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>00101AB8</v>
+        <v>00103CC8</v>
       </c>
       <c r="B93" s="32" t="s">
-        <v>1277</v>
+        <v>1264</v>
       </c>
       <c r="C93" s="32" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="D93" s="32"/>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:5">
       <c r="A94" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>00101ABC</v>
-      </c>
-      <c r="B94" s="32" t="s">
-        <v>1278</v>
+        <v>00103CCC</v>
+      </c>
+      <c r="B94" s="36" t="s">
+        <v>1265</v>
       </c>
       <c r="C94" s="32" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="D94" s="32"/>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:5">
       <c r="A95" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>00101AC0</v>
+        <v>00103CD0</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>1279</v>
+        <v>1266</v>
       </c>
       <c r="C95" s="32" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="D95" s="32"/>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:5">
       <c r="A96" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>00101AC4</v>
+        <v>00103CD4</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>876</v>
+        <v>1267</v>
       </c>
       <c r="C96" s="32" t="s">
-        <v>875</v>
+        <v>1237</v>
       </c>
       <c r="D96" s="32"/>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>00101AC8</v>
+        <v>00103CD8</v>
       </c>
       <c r="B97" s="32" t="s">
-        <v>856</v>
+        <v>1268</v>
       </c>
       <c r="C97" s="32" t="s">
-        <v>848</v>
+        <v>1238</v>
       </c>
       <c r="D97" s="32"/>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="32" t="str">
         <f t="shared" si="2"/>
-        <v>00101ACC</v>
+        <v>00103CDC</v>
       </c>
       <c r="B98" s="32" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C98" s="32" t="str">
-        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E98)-HEX2DEC("6dd000"),8))</f>
+        <v>876</v>
+      </c>
+      <c r="C98" s="32" t="s">
+        <v>875</v>
+      </c>
+      <c r="D98" s="32"/>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>00103CE0</v>
+      </c>
+      <c r="B99" s="32" t="s">
+        <v>856</v>
+      </c>
+      <c r="C99" s="32" t="s">
+        <v>848</v>
+      </c>
+      <c r="D99" s="32"/>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="32" t="str">
+        <f t="shared" si="2"/>
+        <v>00103CE4</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C100" s="32" t="str">
+        <f>_xlfn.CONCAT("bl 0x",DEC2HEX(HEX2DEC(E100)-HEX2DEC("6dd000"),8))</f>
         <v>bl 0x00092ABC</v>
       </c>
-      <c r="D98" s="32"/>
-      <c r="E98" s="8" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>00101AD0</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>1244</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>00101AD4</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>1245</v>
+      <c r="D100" s="32"/>
+      <c r="E100" s="8" t="s">
+        <v>1239</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101AD8</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>1282</v>
+        <v>00103CE8</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>1269</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>1246</v>
+        <v>1241</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101ADC</v>
+        <v>00103CEC</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>1283</v>
+        <v>1270</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101AE0</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>1284</v>
+        <v>00103CF0</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>1271</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101AE4</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>1285</v>
+        <v>00103CF4</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>1272</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101AE8</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>860</v>
+        <v>00103CF8</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>1273</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>834</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101AEC</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>856</v>
+        <v>00103CFC</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>1274</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>848</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101AF0</v>
+        <v>00103D00</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C107" s="8" t="str">
-        <f>SUBSTITUTE(C11,"push","pop")</f>
-        <v>pop {r4, r5, r6, r7, r8, r9, lr}</v>
+        <v>860</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>834</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101AF4</v>
+        <v>00103D04</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>1303</v>
+        <v>856</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>1195</v>
+        <v>848</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101AF8</v>
+        <v>00103D08</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="C109" s="8" t="str">
-        <f>SUBSTITUTE(C107,"lr","pc")</f>
-        <v>pop {r4, r5, r6, r7, r8, r9, pc}</v>
+        <f>SUBSTITUTE(C11,"push","pop")</f>
+        <v>pop {r4, r5, r6, r7, r8, r9, lr}</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="8" t="str">
         <f t="shared" si="2"/>
-        <v>00101AFC</v>
-      </c>
-      <c r="B110" s="9" t="s">
+        <v>00103D0C</v>
+      </c>
+      <c r="B110" s="8" t="s">
         <v>1304</v>
       </c>
-    </row>
-    <row r="113" spans="2:2">
-      <c r="B113" s="9"/>
-    </row>
-    <row r="114" spans="2:2">
-      <c r="B114" s="9"/>
+      <c r="C110" s="8" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>00103D10</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C111" s="8" t="str">
+        <f>SUBSTITUTE(C109,"lr","pc")</f>
+        <v>pop {r4, r5, r6, r7, r8, r9, pc}</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>00103D14</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>1280</v>
+      </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" s="9"/>
     </row>
-    <row r="123" spans="2:2">
-      <c r="B123" s="9"/>
-    </row>
-    <row r="128" spans="2:2">
-      <c r="B128" s="9"/>
+    <row r="116" spans="2:2">
+      <c r="B116" s="9"/>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="9"/>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="9"/>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" s="9"/>
     </row>
-    <row r="131" spans="2:2">
-      <c r="B131" s="9"/>
+    <row r="132" spans="2:2">
+      <c r="B132" s="9"/>
     </row>
     <row r="133" spans="2:2">
       <c r="B133" s="9"/>
     </row>
     <row r="135" spans="2:2">
       <c r="B135" s="9"/>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
